--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161E04F2-A0DB-440E-832A-749B44A0CE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253FFA21-629A-49EE-881E-3A65666E17DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32370" yWindow="780" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32235" yWindow="975" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="402">
   <si>
     <t>SKU</t>
   </si>
@@ -784,15 +784,6 @@
     <t>£53.63</t>
   </si>
   <si>
-    <t>£71.04</t>
-  </si>
-  <si>
-    <t>£95.5</t>
-  </si>
-  <si>
-    <t>£84.22</t>
-  </si>
-  <si>
     <t>£78.5</t>
   </si>
   <si>
@@ -802,15 +793,6 @@
     <t>£79.95</t>
   </si>
   <si>
-    <t>£111.12</t>
-  </si>
-  <si>
-    <t>£153.89</t>
-  </si>
-  <si>
-    <t>£172.26</t>
-  </si>
-  <si>
     <t>£14.99</t>
   </si>
   <si>
@@ -1232,6 +1214,18 @@
   </si>
   <si>
     <t>£54.99</t>
+  </si>
+  <si>
+    <t>£65.56</t>
+  </si>
+  <si>
+    <t>£1777.92</t>
+  </si>
+  <si>
+    <t>£2462.24</t>
+  </si>
+  <si>
+    <t>£2756.16</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1669,7 @@
         <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G2" t="s">
         <v>107</v>
@@ -1702,10 +1696,10 @@
         <v>235</v>
       </c>
       <c r="O2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="P2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="Q2" t="s">
         <v>105</v>
@@ -1731,7 +1725,7 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="G3" t="s">
         <v>108</v>
@@ -1743,7 +1737,7 @@
         <v>154</v>
       </c>
       <c r="J3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="K3" t="s">
         <v>181</v>
@@ -1758,16 +1752,16 @@
         <v>236</v>
       </c>
       <c r="O3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="P3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="Q3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="R3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1787,7 +1781,7 @@
         <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s">
         <v>109</v>
@@ -1799,7 +1793,7 @@
         <v>155</v>
       </c>
       <c r="J4" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="K4" t="s">
         <v>182</v>
@@ -1814,16 +1808,16 @@
         <v>237</v>
       </c>
       <c r="O4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="Q4" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="R4" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1843,7 +1837,7 @@
         <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G5" t="s">
         <v>110</v>
@@ -1855,7 +1849,7 @@
         <v>156</v>
       </c>
       <c r="J5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="K5" t="s">
         <v>183</v>
@@ -1870,16 +1864,16 @@
         <v>238</v>
       </c>
       <c r="O5" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="P5" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="Q5" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="R5" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1899,7 +1893,7 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G6" t="s">
         <v>111</v>
@@ -1911,7 +1905,7 @@
         <v>157</v>
       </c>
       <c r="J6" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="K6" t="s">
         <v>184</v>
@@ -1926,16 +1920,16 @@
         <v>239</v>
       </c>
       <c r="O6" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="P6" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="Q6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="R6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1955,7 +1949,7 @@
         <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="G7" t="s">
         <v>112</v>
@@ -1982,16 +1976,16 @@
         <v>240</v>
       </c>
       <c r="O7" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="P7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="Q7" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="R7" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -2011,7 +2005,7 @@
         <v>82</v>
       </c>
       <c r="F8" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G8" t="s">
         <v>83</v>
@@ -2023,7 +2017,7 @@
         <v>159</v>
       </c>
       <c r="J8" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="K8" t="s">
         <v>186</v>
@@ -2038,16 +2032,16 @@
         <v>241</v>
       </c>
       <c r="O8" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="P8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="Q8" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="R8" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -2067,7 +2061,7 @@
         <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G9" t="s">
         <v>113</v>
@@ -2079,7 +2073,7 @@
         <v>160</v>
       </c>
       <c r="J9" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="K9" t="s">
         <v>187</v>
@@ -2094,16 +2088,16 @@
         <v>242</v>
       </c>
       <c r="O9" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P9" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Q9" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="R9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -2123,7 +2117,7 @@
         <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G10" t="s">
         <v>114</v>
@@ -2135,7 +2129,7 @@
         <v>161</v>
       </c>
       <c r="J10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="K10" t="s">
         <v>188</v>
@@ -2150,16 +2144,16 @@
         <v>243</v>
       </c>
       <c r="O10" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="P10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="Q10" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="R10" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -2179,7 +2173,7 @@
         <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G11" t="s">
         <v>115</v>
@@ -2191,7 +2185,7 @@
         <v>162</v>
       </c>
       <c r="J11" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="K11" t="s">
         <v>189</v>
@@ -2209,13 +2203,13 @@
         <v>85</v>
       </c>
       <c r="P11" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="Q11" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="R11" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -2235,7 +2229,7 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G12" t="s">
         <v>116</v>
@@ -2247,7 +2241,7 @@
         <v>163</v>
       </c>
       <c r="J12" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="K12" t="s">
         <v>190</v>
@@ -2262,16 +2256,16 @@
         <v>245</v>
       </c>
       <c r="O12" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="P12" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="Q12" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="R12" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2291,7 +2285,7 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
         <v>117</v>
@@ -2303,7 +2297,7 @@
         <v>164</v>
       </c>
       <c r="J13" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K13" t="s">
         <v>191</v>
@@ -2318,16 +2312,16 @@
         <v>246</v>
       </c>
       <c r="O13" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="P13" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="Q13" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="R13" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -2347,7 +2341,7 @@
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -2359,7 +2353,7 @@
         <v>165</v>
       </c>
       <c r="J14" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="K14" t="s">
         <v>118</v>
@@ -2374,16 +2368,16 @@
         <v>247</v>
       </c>
       <c r="O14" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="P14" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="Q14" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="R14" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -2403,7 +2397,7 @@
         <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -2415,7 +2409,7 @@
         <v>166</v>
       </c>
       <c r="J15" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="K15" t="s">
         <v>192</v>
@@ -2430,16 +2424,16 @@
         <v>248</v>
       </c>
       <c r="O15" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="P15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="Q15" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="R15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -2471,7 +2465,7 @@
         <v>167</v>
       </c>
       <c r="J16" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K16" t="s">
         <v>193</v>
@@ -2486,13 +2480,13 @@
         <v>249</v>
       </c>
       <c r="O16" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="P16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="Q16" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="R16" t="s">
         <v>105</v>
@@ -2527,7 +2521,7 @@
         <v>168</v>
       </c>
       <c r="J17" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="K17" t="s">
         <v>194</v>
@@ -2542,16 +2536,16 @@
         <v>250</v>
       </c>
       <c r="O17" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="P17" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="Q17" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="R17" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -2571,7 +2565,7 @@
         <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G18" t="s">
         <v>105</v>
@@ -2598,13 +2592,13 @@
         <v>251</v>
       </c>
       <c r="O18" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="P18" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q18" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="R18" t="s">
         <v>105</v>
@@ -2639,7 +2633,7 @@
         <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="K19" t="s">
         <v>196</v>
@@ -2654,16 +2648,16 @@
         <v>252</v>
       </c>
       <c r="O19" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="P19" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="Q19" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="R19" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2683,7 +2677,7 @@
         <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G20" t="s">
         <v>123</v>
@@ -2695,7 +2689,7 @@
         <v>171</v>
       </c>
       <c r="J20" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="K20" t="s">
         <v>197</v>
@@ -2710,16 +2704,16 @@
         <v>253</v>
       </c>
       <c r="O20" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="P20" t="s">
         <v>94</v>
       </c>
       <c r="Q20" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="R20" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2739,7 +2733,7 @@
         <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G21" t="s">
         <v>124</v>
@@ -2751,7 +2745,7 @@
         <v>167</v>
       </c>
       <c r="J21" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="K21" t="s">
         <v>198</v>
@@ -2763,19 +2757,19 @@
         <v>225</v>
       </c>
       <c r="N21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="P21" t="s">
         <v>95</v>
       </c>
       <c r="Q21" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="R21" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2795,7 +2789,7 @@
         <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="G22" t="s">
         <v>125</v>
@@ -2807,7 +2801,7 @@
         <v>172</v>
       </c>
       <c r="J22" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="K22" t="s">
         <v>199</v>
@@ -2819,19 +2813,19 @@
         <v>226</v>
       </c>
       <c r="N22" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O22" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="P22" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q22" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="R22" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2851,7 +2845,7 @@
         <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="G23" t="s">
         <v>126</v>
@@ -2863,7 +2857,7 @@
         <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="K23" t="s">
         <v>200</v>
@@ -2875,19 +2869,19 @@
         <v>227</v>
       </c>
       <c r="N23" t="s">
-        <v>256</v>
+        <v>398</v>
       </c>
       <c r="O23" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="P23" t="s">
         <v>97</v>
       </c>
       <c r="Q23" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="R23" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2907,7 +2901,7 @@
         <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G24" t="s">
         <v>105</v>
@@ -2919,7 +2913,7 @@
         <v>174</v>
       </c>
       <c r="J24" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="K24" t="s">
         <v>201</v>
@@ -2931,7 +2925,7 @@
         <v>228</v>
       </c>
       <c r="N24" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="O24" t="s">
         <v>98</v>
@@ -2940,10 +2934,10 @@
         <v>98</v>
       </c>
       <c r="Q24" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="R24" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2963,7 +2957,7 @@
         <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G25" t="s">
         <v>105</v>
@@ -2975,7 +2969,7 @@
         <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="K25" t="s">
         <v>201</v>
@@ -2987,19 +2981,19 @@
         <v>229</v>
       </c>
       <c r="N25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O25" t="s">
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q25" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="R25" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -3031,7 +3025,7 @@
         <v>105</v>
       </c>
       <c r="J26" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K26" t="s">
         <v>105</v>
@@ -3075,7 +3069,7 @@
         <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G27" t="s">
         <v>105</v>
@@ -3087,7 +3081,7 @@
         <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="K27" t="s">
         <v>202</v>
@@ -3099,19 +3093,19 @@
         <v>231</v>
       </c>
       <c r="N27" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O27" t="s">
         <v>101</v>
       </c>
       <c r="P27" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="Q27" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="R27" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3131,7 +3125,7 @@
         <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G28" t="s">
         <v>105</v>
@@ -3155,19 +3149,19 @@
         <v>232</v>
       </c>
       <c r="N28" t="s">
-        <v>260</v>
+        <v>399</v>
       </c>
       <c r="O28" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="P28" t="s">
         <v>150</v>
       </c>
       <c r="Q28" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="R28" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3187,7 +3181,7 @@
         <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="G29" t="s">
         <v>105</v>
@@ -3211,19 +3205,19 @@
         <v>233</v>
       </c>
       <c r="N29" t="s">
-        <v>261</v>
+        <v>400</v>
       </c>
       <c r="O29" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="P29" t="s">
         <v>151</v>
       </c>
       <c r="Q29" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="R29" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -3243,7 +3237,7 @@
         <v>104</v>
       </c>
       <c r="F30" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G30" t="s">
         <v>105</v>
@@ -3267,10 +3261,10 @@
         <v>234</v>
       </c>
       <c r="N30" t="s">
-        <v>262</v>
+        <v>401</v>
       </c>
       <c r="O30" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="P30" t="s">
         <v>152</v>
@@ -3279,7 +3273,7 @@
         <v>105</v>
       </c>
       <c r="R30" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
